--- a/uploads/processed_5bc040ed-c275-4171-9361-1a6b971278e4.xlsx
+++ b/uploads/processed_5bc040ed-c275-4171-9361-1a6b971278e4.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -945,9 +945,87 @@
         <v/>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>WILLIAM HANKINS</v>
+      </c>
+      <c r="B22" t="str">
+        <v>PROG_EAR@WINDSTREAM.NET</v>
+      </c>
+      <c r="C22" t="str">
+        <v>4090 GREENS DRIVE COLORADO SPRINGS 80922</v>
+      </c>
+      <c r="D22" t="str">
+        <v>4090 Greens Dr</v>
+      </c>
+      <c r="E22">
+        <v>597400</v>
+      </c>
+      <c r="F22" t="str">
+        <v>80922</v>
+      </c>
+      <c r="G22" t="str">
+        <v>https://www.zillow.com/homedetails/4090-Greens-Dr-Colorado-Springs-CO-80922/58405084_zpid/</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>JAMES WU</v>
+      </c>
+      <c r="B23" t="str">
+        <v>JMW1123@SBCGLOBAL.NET</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2064 CHERYL LN VISTA CALIFORNIA 92083</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2064 Cheryl Ln</v>
+      </c>
+      <c r="E23">
+        <v>1035000</v>
+      </c>
+      <c r="F23" t="str">
+        <v>92083</v>
+      </c>
+      <c r="G23" t="str">
+        <v>https://www.zillow.com/homedetails/2064-Cheryl-Ln-Vista-CA-92083/16616773_zpid/</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>JAMES JOHNSON</v>
+      </c>
+      <c r="B24" t="str">
+        <v>JIMJ4645@HOTMAIL.COM</v>
+      </c>
+      <c r="C24" t="str">
+        <v>743 MELODY DR NORTHGLENN COLORADO 802605563</v>
+      </c>
+      <c r="D24" t="str">
+        <v>743 Melody Dr</v>
+      </c>
+      <c r="E24">
+        <v>487300</v>
+      </c>
+      <c r="F24" t="str">
+        <v>80260</v>
+      </c>
+      <c r="G24" t="str">
+        <v>https://www.zillow.com/homedetails/743-Melody-Dr-Northglenn-CO-80260/12974419_zpid/</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H24"/>
   </ignoredErrors>
 </worksheet>
 </file>